--- a/public/CuentasCuentas/Rec-CuentasCuentasSeguidas.xlsx
+++ b/public/CuentasCuentas/Rec-CuentasCuentasSeguidas.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RMartinez\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A1FD22-E234-41A0-A1C5-BEB8DC64E996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2C76AD-C482-4C15-9ED6-868B77BF4B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="74">
   <si>
     <t>cuenta</t>
   </si>
@@ -258,12 +259,6 @@
   </si>
   <si>
     <t>II.1.8 PARTICIPACIONES, APORTACIONES, CONVENIOS, INCENTIVOS DERIVADOS DE LA COLABORACIÓN FISCAL, FONDOS DISTINTOS DE APORTACIONES, TRANSFERENCIAS, ASIGNACIONES, SUBSIDIOS Y SUBVENCIONES, Y PENSIONES Y JUBILACIONES</t>
-  </si>
-  <si>
-    <t>Por el recaudo de otros ingresos propios por pensiones.</t>
-  </si>
-  <si>
-    <t>VII.1.1 (OTROS INGRESOS Y BENEFICIOS)</t>
   </si>
 </sst>
 </file>
@@ -1844,10 +1839,10 @@
         <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>75</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C86" t="s">
+        <v>69</v>
       </c>
       <c r="D86" t="s">
         <v>16</v>
@@ -1858,10 +1853,10 @@
         <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>75</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C87" t="s">
+        <v>69</v>
       </c>
       <c r="D87" t="s">
         <v>33</v>
@@ -1872,10 +1867,10 @@
         <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>75</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C88" t="s">
+        <v>69</v>
       </c>
       <c r="D88" t="s">
         <v>16</v>
@@ -1886,10 +1881,10 @@
         <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C89" t="s">
+        <v>69</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
@@ -1900,10 +1895,10 @@
         <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>75</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C90" t="s">
+        <v>69</v>
       </c>
       <c r="D90" t="s">
         <v>16</v>
@@ -1914,10 +1909,10 @@
         <v>51</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C91" t="s">
+        <v>69</v>
       </c>
       <c r="D91" t="s">
         <v>34</v>
@@ -1928,10 +1923,10 @@
         <v>32</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C92" t="s">
+        <v>69</v>
       </c>
       <c r="D92" t="s">
         <v>16</v>
@@ -1942,10 +1937,10 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>75</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C93" t="s">
+        <v>69</v>
       </c>
       <c r="D93" t="s">
         <v>33</v>
@@ -1956,10 +1951,10 @@
         <v>32</v>
       </c>
       <c r="B94" t="s">
-        <v>75</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C94" t="s">
+        <v>69</v>
       </c>
       <c r="D94" t="s">
         <v>16</v>
@@ -1970,10 +1965,10 @@
         <v>49</v>
       </c>
       <c r="B95" t="s">
-        <v>75</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C95" t="s">
+        <v>69</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
@@ -1984,10 +1979,10 @@
         <v>32</v>
       </c>
       <c r="B96" t="s">
-        <v>75</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C96" t="s">
+        <v>69</v>
       </c>
       <c r="D96" t="s">
         <v>16</v>
@@ -1998,10 +1993,10 @@
         <v>52</v>
       </c>
       <c r="B97" t="s">
-        <v>75</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C97" t="s">
+        <v>69</v>
       </c>
       <c r="D97" t="s">
         <v>34</v>
@@ -2012,10 +2007,10 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>75</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C98" t="s">
+        <v>69</v>
       </c>
       <c r="D98" t="s">
         <v>16</v>
@@ -2026,10 +2021,10 @@
         <v>31</v>
       </c>
       <c r="B99" t="s">
-        <v>75</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C99" t="s">
+        <v>69</v>
       </c>
       <c r="D99" t="s">
         <v>33</v>
@@ -2040,10 +2035,10 @@
         <v>32</v>
       </c>
       <c r="B100" t="s">
-        <v>75</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C100" t="s">
+        <v>69</v>
       </c>
       <c r="D100" t="s">
         <v>16</v>
@@ -2054,10 +2049,10 @@
         <v>49</v>
       </c>
       <c r="B101" t="s">
-        <v>75</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C101" t="s">
+        <v>69</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
@@ -2068,10 +2063,10 @@
         <v>32</v>
       </c>
       <c r="B102" t="s">
-        <v>75</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C102" t="s">
+        <v>69</v>
       </c>
       <c r="D102" t="s">
         <v>16</v>
@@ -2082,10 +2077,10 @@
         <v>53</v>
       </c>
       <c r="B103" t="s">
-        <v>75</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C103" t="s">
+        <v>69</v>
       </c>
       <c r="D103" t="s">
         <v>34</v>
@@ -2096,10 +2091,10 @@
         <v>32</v>
       </c>
       <c r="B104" t="s">
-        <v>75</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C104" t="s">
+        <v>69</v>
       </c>
       <c r="D104" t="s">
         <v>16</v>
@@ -2110,10 +2105,10 @@
         <v>31</v>
       </c>
       <c r="B105" t="s">
-        <v>75</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C105" t="s">
+        <v>69</v>
       </c>
       <c r="D105" t="s">
         <v>33</v>
@@ -2124,10 +2119,10 @@
         <v>32</v>
       </c>
       <c r="B106" t="s">
-        <v>75</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C106" t="s">
+        <v>69</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
@@ -2138,10 +2133,10 @@
         <v>49</v>
       </c>
       <c r="B107" t="s">
-        <v>75</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C107" t="s">
+        <v>69</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
@@ -2152,10 +2147,10 @@
         <v>32</v>
       </c>
       <c r="B108" t="s">
-        <v>75</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C108" t="s">
+        <v>69</v>
       </c>
       <c r="D108" t="s">
         <v>16</v>
@@ -2166,10 +2161,10 @@
         <v>54</v>
       </c>
       <c r="B109" t="s">
-        <v>75</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C109" t="s">
+        <v>69</v>
       </c>
       <c r="D109" t="s">
         <v>34</v>
@@ -2180,10 +2175,10 @@
         <v>32</v>
       </c>
       <c r="B110" t="s">
-        <v>75</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C110" t="s">
+        <v>69</v>
       </c>
       <c r="D110" t="s">
         <v>16</v>
@@ -2194,10 +2189,10 @@
         <v>31</v>
       </c>
       <c r="B111" t="s">
-        <v>75</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C111" t="s">
+        <v>69</v>
       </c>
       <c r="D111" t="s">
         <v>33</v>
@@ -2208,10 +2203,10 @@
         <v>32</v>
       </c>
       <c r="B112" t="s">
-        <v>75</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C112" t="s">
+        <v>69</v>
       </c>
       <c r="D112" t="s">
         <v>16</v>
@@ -2222,10 +2217,10 @@
         <v>49</v>
       </c>
       <c r="B113" t="s">
-        <v>75</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C113" t="s">
+        <v>69</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
@@ -2236,10 +2231,10 @@
         <v>32</v>
       </c>
       <c r="B114" t="s">
-        <v>75</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C114" t="s">
+        <v>69</v>
       </c>
       <c r="D114" t="s">
         <v>16</v>
@@ -2250,10 +2245,10 @@
         <v>55</v>
       </c>
       <c r="B115" t="s">
-        <v>75</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C115" t="s">
+        <v>69</v>
       </c>
       <c r="D115" t="s">
         <v>34</v>
@@ -2264,10 +2259,10 @@
         <v>32</v>
       </c>
       <c r="B116" t="s">
-        <v>75</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C116" t="s">
+        <v>69</v>
       </c>
       <c r="D116" t="s">
         <v>16</v>
@@ -2278,10 +2273,10 @@
         <v>31</v>
       </c>
       <c r="B117" t="s">
-        <v>75</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C117" t="s">
+        <v>69</v>
       </c>
       <c r="D117" t="s">
         <v>33</v>
@@ -2292,10 +2287,10 @@
         <v>32</v>
       </c>
       <c r="B118" t="s">
-        <v>75</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C118" t="s">
+        <v>69</v>
       </c>
       <c r="D118" t="s">
         <v>16</v>
@@ -2306,10 +2301,10 @@
         <v>49</v>
       </c>
       <c r="B119" t="s">
-        <v>75</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C119" t="s">
+        <v>69</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
@@ -2320,10 +2315,10 @@
         <v>32</v>
       </c>
       <c r="B120" t="s">
-        <v>75</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C120" t="s">
+        <v>69</v>
       </c>
       <c r="D120" t="s">
         <v>16</v>
@@ -2334,10 +2329,10 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C121" t="s">
+        <v>69</v>
       </c>
       <c r="D121" t="s">
         <v>34</v>
@@ -2348,10 +2343,10 @@
         <v>32</v>
       </c>
       <c r="B122" t="s">
-        <v>75</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C122" t="s">
+        <v>69</v>
       </c>
       <c r="D122" t="s">
         <v>16</v>
@@ -2362,10 +2357,10 @@
         <v>31</v>
       </c>
       <c r="B123" t="s">
-        <v>75</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C123" t="s">
+        <v>69</v>
       </c>
       <c r="D123" t="s">
         <v>33</v>
@@ -2376,10 +2371,10 @@
         <v>32</v>
       </c>
       <c r="B124" t="s">
-        <v>75</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C124" t="s">
+        <v>69</v>
       </c>
       <c r="D124" t="s">
         <v>16</v>
@@ -2390,10 +2385,10 @@
         <v>49</v>
       </c>
       <c r="B125" t="s">
-        <v>75</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C125" t="s">
+        <v>69</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -2404,10 +2399,10 @@
         <v>32</v>
       </c>
       <c r="B126" t="s">
-        <v>75</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C126" t="s">
+        <v>69</v>
       </c>
       <c r="D126" t="s">
         <v>16</v>
@@ -2418,10 +2413,10 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>75</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C127" t="s">
+        <v>69</v>
       </c>
       <c r="D127" t="s">
         <v>34</v>

--- a/public/CuentasCuentas/Rec-CuentasCuentasSeguidas.xlsx
+++ b/public/CuentasCuentas/Rec-CuentasCuentasSeguidas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\CuentasCuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2C76AD-C482-4C15-9ED6-868B77BF4B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C315238-E4EB-41EB-9A5D-363F48A42B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="106">
   <si>
     <t>cuenta</t>
   </si>
@@ -259,6 +258,102 @@
   </si>
   <si>
     <t>II.1.8 PARTICIPACIONES, APORTACIONES, CONVENIOS, INCENTIVOS DERIVADOS DE LA COLABORACIÓN FISCAL, FONDOS DISTINTOS DE APORTACIONES, TRANSFERENCIAS, ASIGNACIONES, SUBSIDIOS Y SUBVENCIONES, Y PENSIONES Y JUBILACIONES</t>
+  </si>
+  <si>
+    <t>Por la recaudación en efectivo o transferencia de otros ingresos propios derivados de Comisiones por retención en prestaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1.2.02.02 </t>
+  </si>
+  <si>
+    <t>8.1.5.4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>1.1.2.2.02.14</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>Por el recaudo de ingresos de Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.08</t>
+  </si>
+  <si>
+    <t>8.1.5.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.03</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>8.1.5.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.02</t>
+  </si>
+  <si>
+    <t>Por el recaudo de ingresos de Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>Por el recaudo de ingresos de Compensación bancaria de recursos propios</t>
+  </si>
+  <si>
+    <t>8.1.5.4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.04.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.04.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.03.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.06</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.01.02</t>
+  </si>
+  <si>
+    <t>1.1.2.2.02.13</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>2.1.9.1.01.01</t>
   </si>
 </sst>
 </file>
@@ -292,12 +387,24 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -312,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -321,6 +428,8 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A46DBC-EF38-4A4C-B82B-A7E0178DC86F}">
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D351"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
@@ -4102,6 +4211,1450 @@
         <v>34</v>
       </c>
     </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>104</v>
+      </c>
+      <c r="B249" t="s">
+        <v>73</v>
+      </c>
+      <c r="C249" t="s">
+        <v>88</v>
+      </c>
+      <c r="D249" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>89</v>
+      </c>
+      <c r="B250" t="s">
+        <v>73</v>
+      </c>
+      <c r="C250" t="s">
+        <v>88</v>
+      </c>
+      <c r="D250" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>103</v>
+      </c>
+      <c r="B251" t="s">
+        <v>73</v>
+      </c>
+      <c r="C251" t="s">
+        <v>88</v>
+      </c>
+      <c r="D251" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>89</v>
+      </c>
+      <c r="B252" t="s">
+        <v>73</v>
+      </c>
+      <c r="C252" t="s">
+        <v>88</v>
+      </c>
+      <c r="D252" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>50</v>
+      </c>
+      <c r="B253" t="s">
+        <v>73</v>
+      </c>
+      <c r="C253" t="s">
+        <v>88</v>
+      </c>
+      <c r="D253" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>89</v>
+      </c>
+      <c r="B254" t="s">
+        <v>73</v>
+      </c>
+      <c r="C254" t="s">
+        <v>88</v>
+      </c>
+      <c r="D254" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>102</v>
+      </c>
+      <c r="B255" t="s">
+        <v>73</v>
+      </c>
+      <c r="C255" t="s">
+        <v>88</v>
+      </c>
+      <c r="D255" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>89</v>
+      </c>
+      <c r="B256" t="s">
+        <v>73</v>
+      </c>
+      <c r="C256" t="s">
+        <v>88</v>
+      </c>
+      <c r="D256" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>51</v>
+      </c>
+      <c r="B257" t="s">
+        <v>73</v>
+      </c>
+      <c r="C257" t="s">
+        <v>88</v>
+      </c>
+      <c r="D257" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>89</v>
+      </c>
+      <c r="B258" t="s">
+        <v>73</v>
+      </c>
+      <c r="C258" t="s">
+        <v>88</v>
+      </c>
+      <c r="D258" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>59</v>
+      </c>
+      <c r="B259" t="s">
+        <v>73</v>
+      </c>
+      <c r="C259" t="s">
+        <v>88</v>
+      </c>
+      <c r="D259" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>89</v>
+      </c>
+      <c r="B260" t="s">
+        <v>73</v>
+      </c>
+      <c r="C260" t="s">
+        <v>88</v>
+      </c>
+      <c r="D260" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>60</v>
+      </c>
+      <c r="B261" t="s">
+        <v>73</v>
+      </c>
+      <c r="C261" t="s">
+        <v>88</v>
+      </c>
+      <c r="D261" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>89</v>
+      </c>
+      <c r="B262" t="s">
+        <v>73</v>
+      </c>
+      <c r="C262" t="s">
+        <v>88</v>
+      </c>
+      <c r="D262" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>52</v>
+      </c>
+      <c r="B263" t="s">
+        <v>73</v>
+      </c>
+      <c r="C263" t="s">
+        <v>88</v>
+      </c>
+      <c r="D263" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>89</v>
+      </c>
+      <c r="B264" t="s">
+        <v>73</v>
+      </c>
+      <c r="C264" t="s">
+        <v>88</v>
+      </c>
+      <c r="D264" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>101</v>
+      </c>
+      <c r="B265" t="s">
+        <v>73</v>
+      </c>
+      <c r="C265" t="s">
+        <v>88</v>
+      </c>
+      <c r="D265" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>89</v>
+      </c>
+      <c r="B266" t="s">
+        <v>73</v>
+      </c>
+      <c r="C266" t="s">
+        <v>88</v>
+      </c>
+      <c r="D266" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>100</v>
+      </c>
+      <c r="B267" t="s">
+        <v>73</v>
+      </c>
+      <c r="C267" t="s">
+        <v>88</v>
+      </c>
+      <c r="D267" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>89</v>
+      </c>
+      <c r="B268" t="s">
+        <v>73</v>
+      </c>
+      <c r="C268" t="s">
+        <v>88</v>
+      </c>
+      <c r="D268" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>99</v>
+      </c>
+      <c r="B269" t="s">
+        <v>73</v>
+      </c>
+      <c r="C269" t="s">
+        <v>88</v>
+      </c>
+      <c r="D269" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>89</v>
+      </c>
+      <c r="B270" t="s">
+        <v>73</v>
+      </c>
+      <c r="C270" t="s">
+        <v>88</v>
+      </c>
+      <c r="D270" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>53</v>
+      </c>
+      <c r="B271" t="s">
+        <v>73</v>
+      </c>
+      <c r="C271" t="s">
+        <v>88</v>
+      </c>
+      <c r="D271" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>89</v>
+      </c>
+      <c r="B272" t="s">
+        <v>73</v>
+      </c>
+      <c r="C272" t="s">
+        <v>88</v>
+      </c>
+      <c r="D272" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>98</v>
+      </c>
+      <c r="B273" t="s">
+        <v>73</v>
+      </c>
+      <c r="C273" t="s">
+        <v>88</v>
+      </c>
+      <c r="D273" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>89</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D274" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>54</v>
+      </c>
+      <c r="B275" t="s">
+        <v>73</v>
+      </c>
+      <c r="C275" t="s">
+        <v>88</v>
+      </c>
+      <c r="D275" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>89</v>
+      </c>
+      <c r="B276" t="s">
+        <v>73</v>
+      </c>
+      <c r="C276" t="s">
+        <v>88</v>
+      </c>
+      <c r="D276" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>97</v>
+      </c>
+      <c r="B277" t="s">
+        <v>73</v>
+      </c>
+      <c r="C277" t="s">
+        <v>88</v>
+      </c>
+      <c r="D277" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>89</v>
+      </c>
+      <c r="B278" t="s">
+        <v>73</v>
+      </c>
+      <c r="C278" t="s">
+        <v>88</v>
+      </c>
+      <c r="D278" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>96</v>
+      </c>
+      <c r="B279" t="s">
+        <v>73</v>
+      </c>
+      <c r="C279" t="s">
+        <v>88</v>
+      </c>
+      <c r="D279" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>89</v>
+      </c>
+      <c r="B280" t="s">
+        <v>73</v>
+      </c>
+      <c r="C280" t="s">
+        <v>88</v>
+      </c>
+      <c r="D280" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>55</v>
+      </c>
+      <c r="B281" t="s">
+        <v>73</v>
+      </c>
+      <c r="C281" t="s">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>89</v>
+      </c>
+      <c r="B282" t="s">
+        <v>73</v>
+      </c>
+      <c r="C282" t="s">
+        <v>88</v>
+      </c>
+      <c r="D282" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>95</v>
+      </c>
+      <c r="B283" t="s">
+        <v>73</v>
+      </c>
+      <c r="C283" t="s">
+        <v>88</v>
+      </c>
+      <c r="D283" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>89</v>
+      </c>
+      <c r="B284" t="s">
+        <v>73</v>
+      </c>
+      <c r="C284" t="s">
+        <v>88</v>
+      </c>
+      <c r="D284" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>94</v>
+      </c>
+      <c r="B285" t="s">
+        <v>73</v>
+      </c>
+      <c r="C285" t="s">
+        <v>88</v>
+      </c>
+      <c r="D285" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>89</v>
+      </c>
+      <c r="B286" t="s">
+        <v>73</v>
+      </c>
+      <c r="C286" t="s">
+        <v>88</v>
+      </c>
+      <c r="D286" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>93</v>
+      </c>
+      <c r="B287" t="s">
+        <v>73</v>
+      </c>
+      <c r="C287" t="s">
+        <v>88</v>
+      </c>
+      <c r="D287" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>89</v>
+      </c>
+      <c r="B288" t="s">
+        <v>73</v>
+      </c>
+      <c r="C288" t="s">
+        <v>88</v>
+      </c>
+      <c r="D288" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>92</v>
+      </c>
+      <c r="B289" t="s">
+        <v>73</v>
+      </c>
+      <c r="C289" t="s">
+        <v>88</v>
+      </c>
+      <c r="D289" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>89</v>
+      </c>
+      <c r="B290" t="s">
+        <v>73</v>
+      </c>
+      <c r="C290" t="s">
+        <v>88</v>
+      </c>
+      <c r="D290" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>56</v>
+      </c>
+      <c r="B291" t="s">
+        <v>73</v>
+      </c>
+      <c r="C291" t="s">
+        <v>88</v>
+      </c>
+      <c r="D291" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>89</v>
+      </c>
+      <c r="B292" t="s">
+        <v>73</v>
+      </c>
+      <c r="C292" t="s">
+        <v>88</v>
+      </c>
+      <c r="D292" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>91</v>
+      </c>
+      <c r="B293" t="s">
+        <v>73</v>
+      </c>
+      <c r="C293" t="s">
+        <v>88</v>
+      </c>
+      <c r="D293" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>89</v>
+      </c>
+      <c r="B294" t="s">
+        <v>73</v>
+      </c>
+      <c r="C294" t="s">
+        <v>88</v>
+      </c>
+      <c r="D294" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>90</v>
+      </c>
+      <c r="B295" t="s">
+        <v>73</v>
+      </c>
+      <c r="C295" t="s">
+        <v>88</v>
+      </c>
+      <c r="D295" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>89</v>
+      </c>
+      <c r="B296" t="s">
+        <v>73</v>
+      </c>
+      <c r="C296" t="s">
+        <v>88</v>
+      </c>
+      <c r="D296" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>57</v>
+      </c>
+      <c r="B297" t="s">
+        <v>73</v>
+      </c>
+      <c r="C297" t="s">
+        <v>88</v>
+      </c>
+      <c r="D297" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>87</v>
+      </c>
+      <c r="B299" t="s">
+        <v>73</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D299" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B300" t="s">
+        <v>73</v>
+      </c>
+      <c r="D300" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>85</v>
+      </c>
+      <c r="B301" t="s">
+        <v>73</v>
+      </c>
+      <c r="D301" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B302" t="s">
+        <v>73</v>
+      </c>
+      <c r="D302" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>80</v>
+      </c>
+      <c r="B303" t="s">
+        <v>73</v>
+      </c>
+      <c r="D303" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>83</v>
+      </c>
+      <c r="B305" t="s">
+        <v>73</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D305" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B306" t="s">
+        <v>73</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D306" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>82</v>
+      </c>
+      <c r="B307" t="s">
+        <v>73</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D307" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B308" t="s">
+        <v>73</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D308" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>80</v>
+      </c>
+      <c r="B309" t="s">
+        <v>73</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D309" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B310" t="s">
+        <v>73</v>
+      </c>
+      <c r="C310" t="s">
+        <v>74</v>
+      </c>
+      <c r="D310" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>78</v>
+      </c>
+      <c r="B311" t="s">
+        <v>73</v>
+      </c>
+      <c r="C311" t="s">
+        <v>74</v>
+      </c>
+      <c r="D311" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B312" t="s">
+        <v>73</v>
+      </c>
+      <c r="C312" t="s">
+        <v>74</v>
+      </c>
+      <c r="D312" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>77</v>
+      </c>
+      <c r="B313" t="s">
+        <v>73</v>
+      </c>
+      <c r="C313" t="s">
+        <v>74</v>
+      </c>
+      <c r="D313" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B314" t="s">
+        <v>73</v>
+      </c>
+      <c r="C314" t="s">
+        <v>74</v>
+      </c>
+      <c r="D314" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>37</v>
+      </c>
+      <c r="B315" t="s">
+        <v>73</v>
+      </c>
+      <c r="C315" t="s">
+        <v>74</v>
+      </c>
+      <c r="D315" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B316" t="s">
+        <v>73</v>
+      </c>
+      <c r="C316" t="s">
+        <v>74</v>
+      </c>
+      <c r="D316" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>59</v>
+      </c>
+      <c r="B317" t="s">
+        <v>73</v>
+      </c>
+      <c r="C317" t="s">
+        <v>74</v>
+      </c>
+      <c r="D317" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B318" t="s">
+        <v>73</v>
+      </c>
+      <c r="C318" t="s">
+        <v>74</v>
+      </c>
+      <c r="D318" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>75</v>
+      </c>
+      <c r="B319" t="s">
+        <v>73</v>
+      </c>
+      <c r="C319" t="s">
+        <v>74</v>
+      </c>
+      <c r="D319" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B320" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>35</v>
+      </c>
+      <c r="D320" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B321" t="s">
+        <v>4</v>
+      </c>
+      <c r="C321" t="s">
+        <v>35</v>
+      </c>
+      <c r="D321" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B322" t="s">
+        <v>4</v>
+      </c>
+      <c r="C322" t="s">
+        <v>35</v>
+      </c>
+      <c r="D322" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B323" t="s">
+        <v>4</v>
+      </c>
+      <c r="C323" t="s">
+        <v>35</v>
+      </c>
+      <c r="D323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B324" t="s">
+        <v>4</v>
+      </c>
+      <c r="C324" t="s">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B325" t="s">
+        <v>4</v>
+      </c>
+      <c r="C325" t="s">
+        <v>35</v>
+      </c>
+      <c r="D325" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B326" t="s">
+        <v>70</v>
+      </c>
+      <c r="C326" t="s">
+        <v>69</v>
+      </c>
+      <c r="D326" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B327" t="s">
+        <v>70</v>
+      </c>
+      <c r="C327" t="s">
+        <v>69</v>
+      </c>
+      <c r="D327" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B328" t="s">
+        <v>70</v>
+      </c>
+      <c r="C328" t="s">
+        <v>69</v>
+      </c>
+      <c r="D328" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B329" t="s">
+        <v>70</v>
+      </c>
+      <c r="C329" t="s">
+        <v>69</v>
+      </c>
+      <c r="D329" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B330" t="s">
+        <v>70</v>
+      </c>
+      <c r="C330" t="s">
+        <v>69</v>
+      </c>
+      <c r="D330" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B331" t="s">
+        <v>70</v>
+      </c>
+      <c r="C331" t="s">
+        <v>69</v>
+      </c>
+      <c r="D331" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B332" t="s">
+        <v>70</v>
+      </c>
+      <c r="C332" t="s">
+        <v>69</v>
+      </c>
+      <c r="D332" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B333" t="s">
+        <v>70</v>
+      </c>
+      <c r="C333" t="s">
+        <v>69</v>
+      </c>
+      <c r="D333" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B334" t="s">
+        <v>70</v>
+      </c>
+      <c r="C334" t="s">
+        <v>69</v>
+      </c>
+      <c r="D334" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B335" t="s">
+        <v>70</v>
+      </c>
+      <c r="C335" t="s">
+        <v>69</v>
+      </c>
+      <c r="D335" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B336" t="s">
+        <v>70</v>
+      </c>
+      <c r="C336" t="s">
+        <v>69</v>
+      </c>
+      <c r="D336" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B337" t="s">
+        <v>70</v>
+      </c>
+      <c r="C337" t="s">
+        <v>69</v>
+      </c>
+      <c r="D337" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B338" t="s">
+        <v>70</v>
+      </c>
+      <c r="C338" t="s">
+        <v>69</v>
+      </c>
+      <c r="D338" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B339" t="s">
+        <v>70</v>
+      </c>
+      <c r="C339" t="s">
+        <v>69</v>
+      </c>
+      <c r="D339" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B340" t="s">
+        <v>70</v>
+      </c>
+      <c r="C340" t="s">
+        <v>69</v>
+      </c>
+      <c r="D340" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B341" t="s">
+        <v>70</v>
+      </c>
+      <c r="C341" t="s">
+        <v>69</v>
+      </c>
+      <c r="D341" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B342" t="s">
+        <v>70</v>
+      </c>
+      <c r="C342" t="s">
+        <v>69</v>
+      </c>
+      <c r="D342" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B343" t="s">
+        <v>70</v>
+      </c>
+      <c r="C343" t="s">
+        <v>69</v>
+      </c>
+      <c r="D343" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B344" t="s">
+        <v>70</v>
+      </c>
+      <c r="C344" t="s">
+        <v>69</v>
+      </c>
+      <c r="D344" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B345" t="s">
+        <v>70</v>
+      </c>
+      <c r="C345" t="s">
+        <v>69</v>
+      </c>
+      <c r="D345" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B346" t="s">
+        <v>70</v>
+      </c>
+      <c r="C346" t="s">
+        <v>69</v>
+      </c>
+      <c r="D346" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B347" t="s">
+        <v>70</v>
+      </c>
+      <c r="C347" t="s">
+        <v>69</v>
+      </c>
+      <c r="D347" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B348" t="s">
+        <v>73</v>
+      </c>
+      <c r="C348" t="s">
+        <v>72</v>
+      </c>
+      <c r="D348" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B349" t="s">
+        <v>73</v>
+      </c>
+      <c r="C349" t="s">
+        <v>72</v>
+      </c>
+      <c r="D349" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B350" t="s">
+        <v>73</v>
+      </c>
+      <c r="C350" t="s">
+        <v>71</v>
+      </c>
+      <c r="D350" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B351" t="s">
+        <v>73</v>
+      </c>
+      <c r="C351" t="s">
+        <v>71</v>
+      </c>
+      <c r="D351" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
